--- a/YVF_Adoption_Dashboard_CS_HAD.xlsx
+++ b/YVF_Adoption_Dashboard_CS_HAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YVF_Dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC675955-A654-40B7-9473-DF97126DF0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{675D0411-E454-4361-BDE2-9E2E9CFC32FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Booking" sheetId="1" r:id="rId1"/>
@@ -4478,7 +4478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>25</v>
       </c>
